--- a/data-modeling/TMDB 테이블 명세서.xlsx
+++ b/data-modeling/TMDB 테이블 명세서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevPrograms\ktds-28-java-database\data-modeling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA6021F-0609-4E8E-9EC9-E715057DE011}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C713D2E5-621A-454C-A14D-53A7CF6F1C73}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" tabRatio="813" xr2:uid="{802E7722-B099-FB4F-89D0-B5B50B7F50C7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="12150" tabRatio="813" xr2:uid="{802E7722-B099-FB4F-89D0-B5B50B7F50C7}"/>
   </bookViews>
   <sheets>
     <sheet name="영화" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="282">
   <si>
     <t>컬럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1125,6 +1125,38 @@
   </si>
   <si>
     <t>AP-연월일(8자리)-일련번호(6자리)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEL_YN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제 여부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 CHAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'N'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'N': 삭제 안 됨, 'Y': 삭제 됨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-31 유동혁 수정 (2026-08-31 데이터 삭제 회의에 따른 추가)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1291,7 +1323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1337,6 +1369,24 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1355,22 +1405,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -1707,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988B250B-609D-0E4C-BE90-25AD323941FD}">
-  <dimension ref="B1:L22"/>
+  <dimension ref="B1:M23"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="2" customWidth="1"/>
@@ -1720,8 +1755,9 @@
     <col min="9" max="9" width="15.88671875" style="4" customWidth="1"/>
     <col min="10" max="10" width="18.33203125" style="4" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="10.6640625" style="2"/>
+    <col min="12" max="12" width="26.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="10.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1738,19 +1774,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1765,17 +1801,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="5" t="s">
         <v>13</v>
       </c>
@@ -1786,57 +1822,57 @@
         <v>17</v>
       </c>
       <c r="L3" s="14">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="5" t="s">
         <v>1</v>
       </c>
@@ -1849,16 +1885,16 @@
       <c r="F6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -2120,7 +2156,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2146,7 +2182,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2172,7 +2208,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2198,7 +2234,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2224,7 +2260,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2250,7 +2286,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2275,6 +2311,39 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <f t="shared" ref="B23" si="1">IF(C23 &lt;&gt; "", ROW() - 6, "")</f>
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2301,13 +2370,13 @@
           <x14:formula1>
             <xm:f>'Data Dictionary'!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E7:E22</xm:sqref>
+          <xm:sqref>E7:E23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{185F229F-CBAD-1340-B34E-C3CA1B8358A1}">
           <x14:formula1>
             <xm:f>'Data Dictionary'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G7:H22</xm:sqref>
+          <xm:sqref>G7:H23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2348,19 +2417,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -2375,17 +2444,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -2403,50 +2472,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -2459,16 +2528,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -2555,192 +2624,192 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2814,19 +2883,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -2841,17 +2910,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -2869,50 +2938,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -2925,16 +2994,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -3021,192 +3090,192 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5245,19 +5314,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -5272,17 +5341,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -5300,50 +5369,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -5356,16 +5425,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -5422,205 +5491,205 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5694,19 +5763,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -5721,17 +5790,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -5749,50 +5818,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -5805,16 +5874,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -5907,192 +5976,192 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6166,19 +6235,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -6193,17 +6262,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -6221,50 +6290,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -6277,16 +6346,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -6367,195 +6436,195 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6629,19 +6698,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -6656,17 +6725,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -6684,50 +6753,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -6740,16 +6809,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -6894,166 +6963,166 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -7127,19 +7196,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -7154,17 +7223,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -7182,50 +7251,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -7238,16 +7307,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -7366,179 +7435,179 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -7612,19 +7681,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -7639,17 +7708,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -7667,50 +7736,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -7723,16 +7792,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -7789,192 +7858,192 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D23" s="26"/>
+      <c r="D23" s="20"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -8048,19 +8117,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -8075,17 +8144,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -8103,50 +8172,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -8159,16 +8228,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -8261,192 +8330,192 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -8520,19 +8589,19 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
@@ -8547,17 +8616,17 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="9" t="s">
         <v>13</v>
       </c>
@@ -8575,50 +8644,50 @@
       <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
@@ -8631,16 +8700,16 @@
       <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
@@ -8727,192 +8796,192 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
     </row>
     <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="26"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="26"/>
+      <c r="D25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
